--- a/outputs/Block5_Least_Stable.xlsx
+++ b/outputs/Block5_Least_Stable.xlsx
@@ -142,7 +142,7 @@
     <t>RHouLeanResLD  (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>DHouLeanResLR  (&gt;1&lt;=5%)</t>
+    <t>DHouSafResH (&gt;5%&lt;=10%)</t>
   </si>
   <si>
     <t>DSenLikResLR (&gt;5%&lt;=10%)</t>
@@ -636,31 +636,31 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>0.4686639999999987</v>
+        <v>0.4674799999999988</v>
       </c>
       <c r="D2">
-        <v>0.4831359999999993</v>
+        <v>0.4820999999999993</v>
       </c>
       <c r="E2">
-        <v>0.4848653204771308</v>
+        <v>0.4816348617949026</v>
       </c>
       <c r="F2">
         <v>0.484</v>
       </c>
       <c r="G2">
-        <v>0.4749155896970425</v>
+        <v>0.473795522482778</v>
       </c>
       <c r="H2">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="I2">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="L2">
         <v>0.01064148394560983</v>
@@ -675,13 +675,13 @@
         <v>48</v>
       </c>
       <c r="P2">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="S2" t="s">
         <v>49</v>
@@ -696,16 +696,16 @@
         <v>6</v>
       </c>
       <c r="W2">
-        <v>0.4749155896970425</v>
+        <v>0.473795522482778</v>
       </c>
       <c r="X2">
-        <v>0.02479748585957076</v>
+        <v>0.02656335899988149</v>
       </c>
       <c r="Y2">
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>2.330265777434267</v>
+        <v>2.496208154393755</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -714,7 +714,7 @@
         <v>0.2764021804054501</v>
       </c>
       <c r="AC2">
-        <v>21.98801276749871</v>
+        <v>19.73976019256996</v>
       </c>
       <c r="AD2" t="s">
         <v>51</v>
@@ -728,31 +728,31 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>0.5025559999999998</v>
+        <v>0.5035359999999998</v>
       </c>
       <c r="D3">
-        <v>0.4879279999999993</v>
+        <v>0.4889879999999993</v>
       </c>
       <c r="E3">
-        <v>0.4850537176443364</v>
+        <v>0.4880998606769701</v>
       </c>
       <c r="F3">
         <v>0.4868</v>
       </c>
       <c r="G3">
-        <v>0.4962370216909646</v>
+        <v>0.4972515799535244</v>
       </c>
       <c r="H3">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="I3">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="L3">
         <v>0.01323492690170848</v>
@@ -767,13 +767,13 @@
         <v>48</v>
       </c>
       <c r="P3">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="Q3">
         <v>1</v>
       </c>
       <c r="R3">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="S3" t="s">
         <v>49</v>
@@ -788,16 +788,16 @@
         <v>6</v>
       </c>
       <c r="W3">
-        <v>0.4962370216909646</v>
+        <v>0.4972515799535244</v>
       </c>
       <c r="X3">
-        <v>0.02444487447156363</v>
+        <v>0.02631625656357905</v>
       </c>
       <c r="Y3">
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>1.8469973165026</v>
+        <v>1.988394553216756</v>
       </c>
       <c r="AA3">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>0.317384338170467</v>
       </c>
       <c r="AC3">
-        <v>30.10291257195357</v>
+        <v>27.45954213735271</v>
       </c>
       <c r="AD3" t="s">
         <v>51</v>
@@ -820,25 +820,25 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>0.164</v>
+        <v>0.18</v>
       </c>
       <c r="D4">
-        <v>0.268</v>
+        <v>0.264</v>
       </c>
       <c r="E4">
-        <v>0.6905082799680116</v>
+        <v>0.6788079824227848</v>
       </c>
       <c r="F4">
         <v>0.2</v>
       </c>
       <c r="G4">
-        <v>0.2128826077074241</v>
+        <v>0.2194821062252271</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>0.6905082799680116</v>
+        <v>0.6788079824227848</v>
       </c>
       <c r="L4">
         <v>0.4925498319332764</v>
@@ -853,10 +853,10 @@
         <v>48</v>
       </c>
       <c r="P4">
-        <v>0.7880676051329962</v>
+        <v>0.7802977676584159</v>
       </c>
       <c r="Q4">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -865,34 +865,34 @@
         <v>50</v>
       </c>
       <c r="T4">
-        <v>0.09755932516498467</v>
+        <v>0.101489785235631</v>
       </c>
       <c r="U4">
-        <v>0.2119323948670038</v>
+        <v>0.2197022323415841</v>
       </c>
       <c r="V4" t="s">
         <v>6</v>
       </c>
       <c r="W4">
-        <v>0.2128826077074241</v>
+        <v>0.2194821062252271</v>
       </c>
       <c r="X4">
-        <v>0.4776256722605874</v>
+        <v>0.4593258761975577</v>
       </c>
       <c r="Y4">
-        <v>0.3094917200319884</v>
+        <v>0.3211920175772152</v>
       </c>
       <c r="Z4">
-        <v>0.9697002035020272</v>
+        <v>0.9325470163997145</v>
       </c>
       <c r="AA4">
-        <v>0.6283460067730039</v>
+        <v>0.6521005525806892</v>
       </c>
       <c r="AB4">
         <v>1.231374579833191</v>
       </c>
       <c r="AC4">
-        <v>42.73182468197061</v>
+        <v>43.41388982372007</v>
       </c>
       <c r="AD4" t="s">
         <v>52</v>
@@ -906,25 +906,25 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>10.028</v>
+        <v>9.932</v>
       </c>
       <c r="D5">
-        <v>11.468</v>
+        <v>11.352</v>
       </c>
       <c r="E5">
-        <v>13.28203815275881</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="F5">
         <v>11.6</v>
       </c>
       <c r="G5">
-        <v>10.70483610671818</v>
+        <v>10.59943560523598</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>13.28203815275881</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="L5">
         <v>3.050242274051084</v>
@@ -939,10 +939,10 @@
         <v>48</v>
       </c>
       <c r="P5">
-        <v>15.15860750983988</v>
+        <v>14.78818442768141</v>
       </c>
       <c r="Q5">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R5">
         <v>15</v>
@@ -951,34 +951,34 @@
         <v>50</v>
       </c>
       <c r="T5">
-        <v>1.876569357081072</v>
+        <v>1.923431956103332</v>
       </c>
       <c r="U5">
-        <v>-0.158607509839884</v>
+        <v>0.2118155723185868</v>
       </c>
       <c r="V5" t="s">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>10.70483610671818</v>
+        <v>10.59943560523598</v>
       </c>
       <c r="X5">
-        <v>2.577202046040632</v>
+        <v>2.265316866342099</v>
       </c>
       <c r="Y5">
-        <v>1.717961847241188</v>
+        <v>2.135247528421919</v>
       </c>
       <c r="Z5">
-        <v>0.8449171621432557</v>
+        <v>0.7426678482602922</v>
       </c>
       <c r="AA5">
-        <v>0.5632214404266095</v>
+        <v>0.7000255509494521</v>
       </c>
       <c r="AB5">
         <v>0.544686120366265</v>
       </c>
       <c r="AC5">
-        <v>47.41063290551929</v>
+        <v>48.29978656895716</v>
       </c>
       <c r="AD5" t="s">
         <v>52</v>
@@ -992,25 +992,25 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>1.736</v>
+        <v>1.604</v>
       </c>
       <c r="D6">
-        <v>1.98</v>
+        <v>1.924</v>
       </c>
       <c r="E6">
-        <v>0.06755162617559574</v>
+        <v>-0.1313628720128142</v>
       </c>
       <c r="F6">
         <v>2.4</v>
       </c>
       <c r="G6">
-        <v>1.850686118082802</v>
+        <v>1.754408023715151</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>0.06755162617559574</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>1.736334852416627</v>
@@ -1025,10 +1025,10 @@
         <v>48</v>
       </c>
       <c r="P6">
-        <v>0.05816049090560802</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -1037,34 +1037,34 @@
         <v>50</v>
       </c>
       <c r="T6">
-        <v>-0.009391135269987715</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>-0.05816049090560802</v>
+        <v>0</v>
       </c>
       <c r="V6" t="s">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>1.850686118082802</v>
+        <v>1.754408023715151</v>
       </c>
       <c r="X6">
-        <v>1.783134491907207</v>
+        <v>1.754408023715151</v>
       </c>
       <c r="Y6">
-        <v>0.06755162617559574</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1.026953118763609</v>
+        <v>1.010408805233259</v>
       </c>
       <c r="AA6">
-        <v>0.03890472283130038</v>
+        <v>0</v>
       </c>
       <c r="AB6">
         <v>0.5601080169085895</v>
       </c>
       <c r="AC6">
-        <v>50.60417110498163</v>
+        <v>51.85256808577751</v>
       </c>
       <c r="AD6" t="s">
         <v>52</v>
@@ -1078,25 +1078,25 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>13.232</v>
+        <v>13.288</v>
       </c>
       <c r="D7">
-        <v>12.328</v>
+        <v>12.416</v>
       </c>
       <c r="E7">
-        <v>11.23658004704028</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="F7">
         <v>12.4</v>
       </c>
       <c r="G7">
-        <v>12.8070973330047</v>
+        <v>12.87813813537621</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>11.23658004704028</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="L7">
         <v>2.351026032651849</v>
@@ -1111,10 +1111,10 @@
         <v>48</v>
       </c>
       <c r="P7">
-        <v>9.674452691001546</v>
+        <v>9.779145216252848</v>
       </c>
       <c r="Q7">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -1123,34 +1123,34 @@
         <v>50</v>
       </c>
       <c r="T7">
-        <v>-1.562127356038731</v>
+        <v>-1.671300129583011</v>
       </c>
       <c r="U7">
-        <v>0.3255473089984537</v>
+        <v>0.2208547837471517</v>
       </c>
       <c r="V7" t="s">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>12.8070973330047</v>
+        <v>12.87813813537621</v>
       </c>
       <c r="X7">
-        <v>1.570517285964419</v>
+        <v>1.427692789540352</v>
       </c>
       <c r="Y7">
-        <v>1.236580047040277</v>
+        <v>1.45044534583586</v>
       </c>
       <c r="Z7">
-        <v>0.6680135669076143</v>
+        <v>0.6072637094239147</v>
       </c>
       <c r="AA7">
-        <v>0.5259746297430284</v>
+        <v>0.6169414228900835</v>
       </c>
       <c r="AB7">
         <v>0.6530627868477359</v>
       </c>
       <c r="AC7">
-        <v>53.88597538332969</v>
+        <v>54.29973121083951</v>
       </c>
       <c r="AD7" t="s">
         <v>52</v>
@@ -1164,25 +1164,25 @@
         <v>47</v>
       </c>
       <c r="C8">
-        <v>13.58</v>
+        <v>13.548</v>
       </c>
       <c r="D8">
-        <v>14.788</v>
+        <v>14.728</v>
       </c>
       <c r="E8">
-        <v>19.01148659179185</v>
+        <v>18.83927196478475</v>
       </c>
       <c r="F8">
         <v>14.6</v>
       </c>
       <c r="G8">
-        <v>14.16303197882762</v>
+        <v>14.1175179925634</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>19.01148659179185</v>
+        <v>18.83927196478475</v>
       </c>
       <c r="L8">
         <v>5.333756871724871</v>
@@ -1197,10 +1197,10 @@
         <v>48</v>
       </c>
       <c r="P8">
-        <v>19.21302027199633</v>
+        <v>19.20064674567716</v>
       </c>
       <c r="Q8">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R8">
         <v>19</v>
@@ -1209,34 +1209,34 @@
         <v>50</v>
       </c>
       <c r="T8">
-        <v>0.2015336802044807</v>
+        <v>0.3613747808924153</v>
       </c>
       <c r="U8">
-        <v>-0.2130202719963314</v>
+        <v>-0.2006467456771617</v>
       </c>
       <c r="V8" t="s">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>14.16303197882762</v>
+        <v>14.1175179925634</v>
       </c>
       <c r="X8">
-        <v>4.848454612964233</v>
+        <v>4.721753972221347</v>
       </c>
       <c r="Y8">
-        <v>0.01148659179185074</v>
+        <v>0.1607280352152536</v>
       </c>
       <c r="Z8">
-        <v>0.909013052069676</v>
+        <v>0.8852585683558519</v>
       </c>
       <c r="AA8">
-        <v>0.00215356493895383</v>
+        <v>0.03013411354898824</v>
       </c>
       <c r="AB8">
         <v>1.088521810556096</v>
       </c>
       <c r="AC8">
-        <v>55.34343008256245</v>
+        <v>55.65685088619063</v>
       </c>
       <c r="AD8" t="s">
         <v>52</v>
@@ -1250,25 +1250,25 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1.084</v>
+        <v>1.12</v>
       </c>
       <c r="D9">
-        <v>1.172</v>
+        <v>1.168</v>
       </c>
       <c r="E9">
-        <v>1.761149755943273</v>
+        <v>1.780416614874208</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>1.125362206521666</v>
+        <v>1.142561203557273</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>1.761149755943273</v>
+        <v>1.780416614874208</v>
       </c>
       <c r="L9">
         <v>0.8500971208676269</v>
@@ -1283,10 +1283,10 @@
         <v>48</v>
       </c>
       <c r="P9">
-        <v>2.00997599986936</v>
+        <v>2.046609860316908</v>
       </c>
       <c r="Q9">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R9">
         <v>2</v>
@@ -1295,34 +1295,34 @@
         <v>50</v>
       </c>
       <c r="T9">
-        <v>0.2488262439260871</v>
+        <v>0.2661932454427003</v>
       </c>
       <c r="U9">
-        <v>-0.009975999869360042</v>
+        <v>-0.04660986031690806</v>
       </c>
       <c r="V9" t="s">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>1.125362206521666</v>
+        <v>1.142561203557273</v>
       </c>
       <c r="X9">
-        <v>0.6357875494216065</v>
+        <v>0.6378554113169352</v>
       </c>
       <c r="Y9">
-        <v>0.2388502440567271</v>
+        <v>0.2195833851257922</v>
       </c>
       <c r="Z9">
-        <v>0.7478998973349168</v>
+        <v>0.7503323980981451</v>
       </c>
       <c r="AA9">
-        <v>0.2809681837446426</v>
+        <v>0.2583038805044779</v>
       </c>
       <c r="AB9">
         <v>1.700194241735254</v>
       </c>
       <c r="AC9">
-        <v>55.73990894075605</v>
+        <v>56.09506097814787</v>
       </c>
       <c r="AD9" t="s">
         <v>52</v>
@@ -1336,25 +1336,25 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>0.552</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D10">
-        <v>0.392</v>
+        <v>0.408</v>
       </c>
       <c r="E10">
-        <v>0.2703407362038964</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="F10">
         <v>0.4</v>
       </c>
       <c r="G10">
-        <v>0.4767959881424244</v>
+        <v>0.4885561887353032</v>
       </c>
       <c r="J10" t="s">
         <v>4</v>
       </c>
       <c r="K10">
-        <v>0.2703407362038964</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="L10">
         <v>0.3921195507989373</v>
@@ -1369,10 +1369,10 @@
         <v>48</v>
       </c>
       <c r="P10">
-        <v>0.3085361649247209</v>
+        <v>0.3618566504167141</v>
       </c>
       <c r="Q10">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -1381,34 +1381,34 @@
         <v>50</v>
       </c>
       <c r="T10">
-        <v>0.03819542872082443</v>
+        <v>0.04706505036799469</v>
       </c>
       <c r="U10">
-        <v>-0.3085361649247209</v>
+        <v>-0.3618566504167141</v>
       </c>
       <c r="V10" t="s">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>0.4767959881424244</v>
+        <v>0.4885561887353032</v>
       </c>
       <c r="X10">
-        <v>0.206455251938528</v>
+        <v>0.1737645886865837</v>
       </c>
       <c r="Y10">
-        <v>0.2703407362038964</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="Z10">
-        <v>0.526510987574781</v>
+        <v>0.4431418640884933</v>
       </c>
       <c r="AA10">
-        <v>0.6894344738819614</v>
+        <v>0.8027949624223952</v>
       </c>
       <c r="AB10">
         <v>0.6535325846648956</v>
       </c>
       <c r="AC10">
-        <v>55.79230620253968</v>
+        <v>56.60796713936882</v>
       </c>
       <c r="AD10" t="s">
         <v>52</v>
@@ -1422,25 +1422,25 @@
         <v>46</v>
       </c>
       <c r="C11">
-        <v>0.716</v>
+        <v>0.74</v>
       </c>
       <c r="D11">
-        <v>0.66</v>
+        <v>0.672</v>
       </c>
       <c r="E11">
-        <v>0.9608490161719081</v>
+        <v>0.9935995824715044</v>
       </c>
       <c r="F11">
         <v>0.6</v>
       </c>
       <c r="G11">
-        <v>0.6896785958498485</v>
+        <v>0.7080382949605304</v>
       </c>
       <c r="J11" t="s">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>0.9608490161719081</v>
+        <v>0.9935995824715044</v>
       </c>
       <c r="L11">
         <v>0.3332002265469857</v>
@@ -1455,10 +1455,10 @@
         <v>48</v>
       </c>
       <c r="P11">
-        <v>1.096603770057717</v>
+        <v>1.14215441807513</v>
       </c>
       <c r="Q11">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -1467,34 +1467,34 @@
         <v>50</v>
       </c>
       <c r="T11">
-        <v>0.135754753885809</v>
+        <v>0.1485548356036258</v>
       </c>
       <c r="U11">
-        <v>-0.09660377005771714</v>
+        <v>-0.1421544180751302</v>
       </c>
       <c r="V11" t="s">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>0.6896785958498485</v>
+        <v>0.7080382949605304</v>
       </c>
       <c r="X11">
-        <v>0.2711704203220596</v>
+        <v>0.285561287510974</v>
       </c>
       <c r="Y11">
-        <v>0.0391509838280919</v>
+        <v>0.006400417528495628</v>
       </c>
       <c r="Z11">
-        <v>0.813836242346675</v>
+        <v>0.8570260904990893</v>
       </c>
       <c r="AA11">
-        <v>0.1174998715751806</v>
+        <v>0.01920892309955583</v>
       </c>
       <c r="AB11">
         <v>0.5553337109116429</v>
       </c>
       <c r="AC11">
-        <v>56.54584207939454</v>
+        <v>56.90482321607101</v>
       </c>
       <c r="AD11" t="s">
         <v>52</v>
@@ -1508,25 +1508,25 @@
         <v>47</v>
       </c>
       <c r="C12">
-        <v>1.832</v>
+        <v>1.904</v>
       </c>
       <c r="D12">
-        <v>1.772</v>
+        <v>1.796</v>
       </c>
       <c r="E12">
-        <v>2.554644495322226</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="F12">
         <v>1.6</v>
       </c>
       <c r="G12">
-        <v>1.803041458005251</v>
+        <v>1.851874624409452</v>
       </c>
       <c r="J12" t="s">
         <v>4</v>
       </c>
       <c r="K12">
-        <v>2.554644495322226</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="L12">
         <v>1.198624596172324</v>
@@ -1541,46 +1541,46 @@
         <v>48</v>
       </c>
       <c r="P12">
-        <v>2.528722469358031</v>
+        <v>2.557215395085126</v>
       </c>
       <c r="Q12">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12" t="s">
         <v>50</v>
       </c>
       <c r="T12">
-        <v>-0.02592202596419435</v>
+        <v>-0.04703542507679881</v>
       </c>
       <c r="U12">
-        <v>-0.5287224693580312</v>
+        <v>0.4427846049148738</v>
       </c>
       <c r="V12" t="s">
         <v>6</v>
       </c>
       <c r="W12">
-        <v>1.803041458005251</v>
+        <v>1.851874624409452</v>
       </c>
       <c r="X12">
-        <v>0.7516030373169746</v>
+        <v>0.7523761957524733</v>
       </c>
       <c r="Y12">
-        <v>0.5546444953222256</v>
+        <v>0.395749179838075</v>
       </c>
       <c r="Z12">
-        <v>0.627054575483547</v>
+        <v>0.6276996135029299</v>
       </c>
       <c r="AA12">
-        <v>0.4627341179994319</v>
+        <v>0.3301694134275707</v>
       </c>
       <c r="AB12">
         <v>0.7491403726077025</v>
       </c>
       <c r="AC12">
-        <v>56.57842736664286</v>
+        <v>59.24054223283283</v>
       </c>
       <c r="AD12" t="s">
         <v>52</v>
@@ -1594,25 +1594,25 @@
         <v>47</v>
       </c>
       <c r="C13">
-        <v>8.612</v>
+        <v>8.763999999999999</v>
       </c>
       <c r="D13">
-        <v>6.564</v>
+        <v>6.752</v>
       </c>
       <c r="E13">
-        <v>3.808811132083866</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="F13">
         <v>6.6</v>
       </c>
       <c r="G13">
-        <v>7.623548433245896</v>
+        <v>7.792923558442745</v>
       </c>
       <c r="J13" t="s">
         <v>4</v>
       </c>
       <c r="K13">
-        <v>3.808811132083866</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="L13">
         <v>4.673523904256721</v>
@@ -1627,10 +1627,10 @@
         <v>48</v>
       </c>
       <c r="P13">
-        <v>3.770163053558897</v>
+        <v>4.224092654695784</v>
       </c>
       <c r="Q13">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R13">
         <v>4</v>
@@ -1639,37 +1639,37 @@
         <v>50</v>
       </c>
       <c r="T13">
-        <v>-0.03864807852496854</v>
+        <v>-0.07769466504826283</v>
       </c>
       <c r="U13">
-        <v>0.229836946441103</v>
+        <v>-0.2240926546957844</v>
       </c>
       <c r="V13" t="s">
         <v>6</v>
       </c>
       <c r="W13">
-        <v>7.623548433245896</v>
+        <v>7.792923558442745</v>
       </c>
       <c r="X13">
-        <v>3.81473730116203</v>
+        <v>3.491136238698697</v>
       </c>
       <c r="Y13">
-        <v>0.1911888679161344</v>
+        <v>0.3017873197440473</v>
       </c>
       <c r="Z13">
-        <v>0.816244311425797</v>
+        <v>0.747002970396474</v>
       </c>
       <c r="AA13">
-        <v>0.04090893121184135</v>
+        <v>0.06457382607354901</v>
       </c>
       <c r="AB13">
         <v>0.5563718933638954</v>
       </c>
       <c r="AC13">
-        <v>57.99131498158366</v>
+        <v>60.16058574846904</v>
       </c>
       <c r="AD13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:30">
@@ -1680,79 +1680,79 @@
         <v>47</v>
       </c>
       <c r="C14">
-        <v>3.54</v>
+        <v>173.496</v>
       </c>
       <c r="D14">
-        <v>4.812</v>
+        <v>170.784</v>
       </c>
       <c r="E14">
-        <v>5.586198698614951</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>169.2</v>
       </c>
       <c r="G14">
-        <v>4.153921090288683</v>
+        <v>172.1870739018374</v>
       </c>
       <c r="J14" t="s">
         <v>4</v>
       </c>
       <c r="K14">
-        <v>5.586198698614951</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="L14">
-        <v>2.262338789582505</v>
+        <v>4.764861070548267</v>
       </c>
       <c r="M14">
         <v>5.24749619700716</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>13.2</v>
       </c>
       <c r="O14" t="s">
         <v>48</v>
       </c>
       <c r="P14">
-        <v>5.645415907992541</v>
+        <v>176.9807039529099</v>
       </c>
       <c r="Q14">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R14">
-        <v>6</v>
+        <v>177</v>
       </c>
       <c r="S14" t="s">
         <v>50</v>
       </c>
       <c r="T14">
-        <v>0.05921720937758934</v>
+        <v>3.330948376911721</v>
       </c>
       <c r="U14">
-        <v>0.3545840920074594</v>
+        <v>0.01929604709013688</v>
       </c>
       <c r="V14" t="s">
         <v>6</v>
       </c>
       <c r="W14">
-        <v>4.153921090288683</v>
+        <v>172.1870739018374</v>
       </c>
       <c r="X14">
-        <v>1.432277608326268</v>
+        <v>1.462681674160791</v>
       </c>
       <c r="Y14">
-        <v>0.4138013013850488</v>
+        <v>3.350244424001858</v>
       </c>
       <c r="Z14">
-        <v>0.633095986737947</v>
+        <v>0.3069725753814032</v>
       </c>
       <c r="AA14">
-        <v>0.1829086356519627</v>
+        <v>0.7031148179135396</v>
       </c>
       <c r="AB14">
-        <v>0.452467757916501</v>
+        <v>0.3609743235263839</v>
       </c>
       <c r="AC14">
-        <v>62.15552874778314</v>
+        <v>64.04255765445993</v>
       </c>
       <c r="AD14" t="s">
         <v>53</v>
@@ -1766,19 +1766,19 @@
         <v>46</v>
       </c>
       <c r="C15">
-        <v>0.676</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="D15">
-        <v>0.612</v>
+        <v>0.608</v>
       </c>
       <c r="E15">
-        <v>-0.005331174175850051</v>
+        <v>-0.01550360442781762</v>
       </c>
       <c r="F15">
         <v>0.6</v>
       </c>
       <c r="G15">
-        <v>0.6459183952569697</v>
+        <v>0.6503979940712121</v>
       </c>
       <c r="J15" t="s">
         <v>4</v>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1820,16 +1820,16 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>0.6459183952569697</v>
+        <v>0.6503979940712121</v>
       </c>
       <c r="X15">
-        <v>0.6459183952569697</v>
+        <v>0.6503979940712121</v>
       </c>
       <c r="Y15">
         <v>0</v>
       </c>
       <c r="Z15">
-        <v>0.642420983273117</v>
+        <v>0.6468763266973739</v>
       </c>
       <c r="AA15">
         <v>0</v>
@@ -1838,7 +1838,7 @@
         <v>1.117160124789949</v>
       </c>
       <c r="AC15">
-        <v>65.86429881671735</v>
+        <v>65.67383349516004</v>
       </c>
       <c r="AD15" t="s">
         <v>53</v>
@@ -1852,25 +1852,25 @@
         <v>46</v>
       </c>
       <c r="C16">
-        <v>0.368</v>
+        <v>0.38</v>
       </c>
       <c r="D16">
-        <v>0.512</v>
+        <v>0.496</v>
       </c>
       <c r="E16">
-        <v>0.8003007397713651</v>
+        <v>0.7868170324027036</v>
       </c>
       <c r="F16">
         <v>0.4</v>
       </c>
       <c r="G16">
-        <v>0.4356836106718179</v>
+        <v>0.4345229085967423</v>
       </c>
       <c r="J16" t="s">
         <v>4</v>
       </c>
       <c r="K16">
-        <v>0.8003007397713651</v>
+        <v>0.7868170324027036</v>
       </c>
       <c r="L16">
         <v>0.8079772006265793</v>
@@ -1885,10 +1885,10 @@
         <v>48</v>
       </c>
       <c r="P16">
-        <v>0.689041649067501</v>
+        <v>0.6719736906377493</v>
       </c>
       <c r="Q16">
-        <v>0.8609783982760665</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -1897,34 +1897,34 @@
         <v>50</v>
       </c>
       <c r="T16">
-        <v>-0.1112590907038641</v>
+        <v>-0.1148433417649544</v>
       </c>
       <c r="U16">
-        <v>0.310958350932499</v>
+        <v>0.3280263093622507</v>
       </c>
       <c r="V16" t="s">
         <v>6</v>
       </c>
       <c r="W16">
-        <v>0.4356836106718179</v>
+        <v>0.4345229085967423</v>
       </c>
       <c r="X16">
-        <v>0.3646171290995471</v>
+        <v>0.3522941238059614</v>
       </c>
       <c r="Y16">
-        <v>0.1996992602286349</v>
+        <v>0.2131829675972964</v>
       </c>
       <c r="Z16">
-        <v>0.4512715566934187</v>
+        <v>0.4360198821609822</v>
       </c>
       <c r="AA16">
-        <v>0.247159523899647</v>
+        <v>0.2638477514365193</v>
       </c>
       <c r="AB16">
         <v>1.346628667710966</v>
       </c>
       <c r="AC16">
-        <v>68.39760714610466</v>
+        <v>68.6767387081441</v>
       </c>
       <c r="AD16" t="s">
         <v>53</v>

--- a/outputs/Block5_Least_Stable.xlsx
+++ b/outputs/Block5_Least_Stable.xlsx
@@ -109,46 +109,46 @@
     <t>RPP</t>
   </si>
   <si>
+    <t>RSenTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>RSenLikResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
     <t>DPP</t>
   </si>
   <si>
-    <t>RSenTiltResH (&lt;=1%)</t>
+    <t>DSenSafResH (&gt;10%)</t>
+  </si>
+  <si>
+    <t>RSenLikResLD (&gt;5%&lt;=10%)</t>
   </si>
   <si>
     <t>RSenSafResH (&gt;10%)</t>
   </si>
   <si>
+    <t>DSenTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DSenTiltResLR (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DSenLikResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>DSenLikResLR (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>RSenLeanResLD  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
     <t>DSenSafResLR (&gt;10%)</t>
   </si>
   <si>
-    <t>DSenSafResH (&gt;10%)</t>
-  </si>
-  <si>
-    <t>DHouLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RSenLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RSenLikResLD (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RSenLeanResLD  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>RHouTiltResLD (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>RHouLeanResLD  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>DHouSafResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>DSenLikResLR (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>DSenTiltResH (&lt;=1%)</t>
+    <t>DSenLeanResH  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>DSenLeanResLR  (&gt;1&lt;=5%)</t>
   </si>
   <si>
     <t>Popular Vote</t>
@@ -157,9 +157,6 @@
     <t>Senate Buckets</t>
   </si>
   <si>
-    <t>House Buckets</t>
-  </si>
-  <si>
     <t>ML Predicted</t>
   </si>
   <si>
@@ -176,6 +173,9 @@
   </si>
   <si>
     <t>Moderate sensitivity</t>
+  </si>
+  <si>
+    <t>Moderate-low sensitivity</t>
   </si>
 </sst>
 </file>
@@ -636,19 +636,19 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>0.4674799999999988</v>
+        <v>0.4593799999999982</v>
       </c>
       <c r="D2">
-        <v>0.4820999999999993</v>
+        <v>0.4739999999999988</v>
       </c>
       <c r="E2">
-        <v>0.4816348617949026</v>
+        <v>0.4731870983260868</v>
       </c>
       <c r="F2">
         <v>0.484</v>
       </c>
       <c r="G2">
-        <v>0.473795522482778</v>
+        <v>0.4653280968183968</v>
       </c>
       <c r="H2">
         <v>0.4472321634828965</v>
@@ -672,7 +672,7 @@
         <v>0.0385</v>
       </c>
       <c r="O2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P2">
         <v>0.4472321634828965</v>
@@ -684,7 +684,7 @@
         <v>0.4472321634828965</v>
       </c>
       <c r="S2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -696,16 +696,16 @@
         <v>6</v>
       </c>
       <c r="W2">
-        <v>0.473795522482778</v>
+        <v>0.4653280968183968</v>
       </c>
       <c r="X2">
-        <v>0.02656335899988149</v>
+        <v>0.01809593333550036</v>
       </c>
       <c r="Y2">
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>2.496208154393755</v>
+        <v>1.700508446753414</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -714,10 +714,10 @@
         <v>0.2764021804054501</v>
       </c>
       <c r="AC2">
-        <v>19.73976019256996</v>
+        <v>33.11014383145091</v>
       </c>
       <c r="AD2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:30">
@@ -725,91 +725,85 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3">
-        <v>0.5035359999999998</v>
+        <v>0.132</v>
       </c>
       <c r="D3">
-        <v>0.4889879999999993</v>
+        <v>0.236</v>
       </c>
       <c r="E3">
-        <v>0.4880998606769701</v>
+        <v>0.6297196965274399</v>
       </c>
       <c r="F3">
-        <v>0.4868</v>
+        <v>0.2</v>
       </c>
       <c r="G3">
-        <v>0.4972515799535244</v>
-      </c>
-      <c r="H3">
-        <v>0.5235678365171035</v>
-      </c>
-      <c r="I3">
-        <v>0.5235678365171035</v>
+        <v>0.1794951897484802</v>
       </c>
       <c r="J3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>0.5235678365171035</v>
+        <v>0.6297196965274399</v>
       </c>
       <c r="L3">
-        <v>0.01323492690170848</v>
+        <v>0.4196830443219419</v>
       </c>
       <c r="M3">
-        <v>0.01193820542365915</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N3">
-        <v>0.04170000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="O3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P3">
-        <v>0.5235678365171035</v>
+        <v>0.7759837911047821</v>
       </c>
       <c r="Q3">
+        <v>1.232268571848568</v>
+      </c>
+      <c r="R3">
         <v>1</v>
-      </c>
-      <c r="R3">
-        <v>0.5235678365171035</v>
       </c>
       <c r="S3" t="s">
         <v>49</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.1462640945773422</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.2240162088952179</v>
       </c>
       <c r="V3" t="s">
         <v>6</v>
       </c>
       <c r="W3">
-        <v>0.4972515799535244</v>
+        <v>0.1794951897484802</v>
       </c>
       <c r="X3">
-        <v>0.02631625656357905</v>
+        <v>0.4502245067789596</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>0.3702803034725601</v>
       </c>
       <c r="Z3">
-        <v>1.988394553216756</v>
+        <v>1.072772686126412</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.8822855926209767</v>
       </c>
       <c r="AB3">
-        <v>0.317384338170467</v>
+        <v>1.049207610804855</v>
       </c>
       <c r="AC3">
-        <v>27.45954213735271</v>
+        <v>36.56414014265842</v>
       </c>
       <c r="AD3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -820,82 +814,82 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>0.18</v>
+        <v>1.124</v>
       </c>
       <c r="D4">
-        <v>0.264</v>
+        <v>1.14</v>
       </c>
       <c r="E4">
-        <v>0.6788079824227848</v>
+        <v>1.941748773991384</v>
       </c>
       <c r="F4">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0.2194821062252271</v>
+        <v>1.131306952268997</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>0.6788079824227848</v>
+        <v>1.941748773991384</v>
       </c>
       <c r="L4">
-        <v>0.4925498319332764</v>
+        <v>0.5888547436899401</v>
       </c>
       <c r="M4">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N4">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P4">
-        <v>0.7802977676584159</v>
+        <v>2.392755988615071</v>
       </c>
       <c r="Q4">
-        <v>1.149511773378675</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T4">
-        <v>0.101489785235631</v>
+        <v>0.4510072146236872</v>
       </c>
       <c r="U4">
-        <v>0.2197022323415841</v>
+        <v>-0.3927559886150713</v>
       </c>
       <c r="V4" t="s">
         <v>6</v>
       </c>
       <c r="W4">
-        <v>0.2194821062252271</v>
+        <v>1.131306952268997</v>
       </c>
       <c r="X4">
-        <v>0.4593258761975577</v>
+        <v>0.8104418217223872</v>
       </c>
       <c r="Y4">
-        <v>0.3211920175772152</v>
+        <v>0.05825122600861588</v>
       </c>
       <c r="Z4">
-        <v>0.9325470163997145</v>
+        <v>1.376301762713019</v>
       </c>
       <c r="AA4">
-        <v>0.6521005525806892</v>
+        <v>0.09892291203021693</v>
       </c>
       <c r="AB4">
-        <v>1.231374579833191</v>
+        <v>1.17770948737988</v>
       </c>
       <c r="AC4">
-        <v>43.41388982372007</v>
+        <v>39.4861912039952</v>
       </c>
       <c r="AD4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -903,85 +897,91 @@
         <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5">
-        <v>9.932</v>
+        <v>0.5128880000000006</v>
       </c>
       <c r="D5">
-        <v>11.352</v>
+        <v>0.4971799999999998</v>
       </c>
       <c r="E5">
-        <v>12.86475247157808</v>
+        <v>0.4974436169072992</v>
       </c>
       <c r="F5">
-        <v>11.6</v>
+        <v>0.4868</v>
       </c>
       <c r="G5">
-        <v>10.59943560523598</v>
+        <v>0.5064972541160466</v>
+      </c>
+      <c r="H5">
+        <v>0.5235678365171035</v>
+      </c>
+      <c r="I5">
+        <v>0.5235678365171035</v>
       </c>
       <c r="J5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>12.86475247157808</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="L5">
-        <v>3.050242274051084</v>
+        <v>0.01323492690170848</v>
       </c>
       <c r="M5">
-        <v>1.038416113387647</v>
+        <v>0.01193820542365915</v>
       </c>
       <c r="N5">
-        <v>5.6</v>
+        <v>0.04170000000000001</v>
       </c>
       <c r="O5" t="s">
+        <v>47</v>
+      </c>
+      <c r="P5">
+        <v>0.5235678365171035</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0.5235678365171035</v>
+      </c>
+      <c r="S5" t="s">
         <v>48</v>
       </c>
-      <c r="P5">
-        <v>14.78818442768141</v>
-      </c>
-      <c r="Q5">
-        <v>1.149511773378675</v>
-      </c>
-      <c r="R5">
-        <v>15</v>
-      </c>
-      <c r="S5" t="s">
-        <v>50</v>
-      </c>
       <c r="T5">
-        <v>1.923431956103332</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>0.2118155723185868</v>
+        <v>0</v>
       </c>
       <c r="V5" t="s">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>10.59943560523598</v>
+        <v>0.5064972541160466</v>
       </c>
       <c r="X5">
-        <v>2.265316866342099</v>
+        <v>0.01707058240105686</v>
       </c>
       <c r="Y5">
-        <v>2.135247528421919</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>0.7426678482602922</v>
+        <v>1.289813123097283</v>
       </c>
       <c r="AA5">
-        <v>0.7000255509494521</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.544686120366265</v>
+        <v>0.317384338170467</v>
       </c>
       <c r="AC5">
-        <v>48.29978656895716</v>
+        <v>43.24110969117353</v>
       </c>
       <c r="AD5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -992,82 +992,82 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>1.604</v>
+        <v>14.476</v>
       </c>
       <c r="D6">
-        <v>1.924</v>
+        <v>13.084</v>
       </c>
       <c r="E6">
-        <v>-0.1313628720128142</v>
+        <v>12.1475539711821</v>
       </c>
       <c r="F6">
-        <v>2.4</v>
+        <v>12.4</v>
       </c>
       <c r="G6">
-        <v>1.754408023715151</v>
+        <v>13.84029515259726</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>12.1475539711821</v>
       </c>
       <c r="L6">
-        <v>1.736334852416627</v>
+        <v>2.777213034732671</v>
       </c>
       <c r="M6">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>9.555673875500363</v>
       </c>
       <c r="Q6">
-        <v>0.8540406002469759</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>-2.591880095681738</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>-0.5556738755003625</v>
       </c>
       <c r="V6" t="s">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>1.754408023715151</v>
+        <v>13.84029515259726</v>
       </c>
       <c r="X6">
-        <v>1.754408023715151</v>
+        <v>1.692741181415164</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>3.1475539711821</v>
       </c>
       <c r="Z6">
-        <v>1.010408805233259</v>
+        <v>0.6095107434126327</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.133349848145545</v>
       </c>
       <c r="AB6">
-        <v>0.5601080169085895</v>
+        <v>0.7714480652035196</v>
       </c>
       <c r="AC6">
-        <v>51.85256808577751</v>
+        <v>45.25511742057672</v>
       </c>
       <c r="AD6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -1078,82 +1078,82 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>13.288</v>
+        <v>0.764</v>
       </c>
       <c r="D7">
-        <v>12.416</v>
+        <v>0.532</v>
       </c>
       <c r="E7">
-        <v>11.45044534583586</v>
+        <v>0.4302454583585212</v>
       </c>
       <c r="F7">
-        <v>12.4</v>
+        <v>0.4</v>
       </c>
       <c r="G7">
-        <v>12.87813813537621</v>
+        <v>0.6580491920995442</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>11.45044534583586</v>
+        <v>0.4302454583585212</v>
       </c>
       <c r="L7">
-        <v>2.351026032651849</v>
+        <v>0.4552884680086201</v>
       </c>
       <c r="M7">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="O7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P7">
-        <v>9.779145216252848</v>
+        <v>0.5301779565157876</v>
       </c>
       <c r="Q7">
-        <v>0.8540406002469759</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T7">
-        <v>-1.671300129583011</v>
+        <v>0.09993249815726635</v>
       </c>
       <c r="U7">
-        <v>0.2208547837471517</v>
+        <v>0.4698220434842124</v>
       </c>
       <c r="V7" t="s">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>12.87813813537621</v>
+        <v>0.6580491920995442</v>
       </c>
       <c r="X7">
-        <v>1.427692789540352</v>
+        <v>0.2278037337410229</v>
       </c>
       <c r="Y7">
-        <v>1.45044534583586</v>
+        <v>0.5697545416414788</v>
       </c>
       <c r="Z7">
-        <v>0.6072637094239147</v>
+        <v>0.5003503267662599</v>
       </c>
       <c r="AA7">
-        <v>0.6169414228900835</v>
+        <v>1.251414392579545</v>
       </c>
       <c r="AB7">
-        <v>0.6530627868477359</v>
+        <v>0.7588141133477002</v>
       </c>
       <c r="AC7">
-        <v>54.29973121083951</v>
+        <v>46.61616811374733</v>
       </c>
       <c r="AD7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1161,85 +1161,85 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8">
-        <v>13.548</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="D8">
-        <v>14.728</v>
+        <v>10.476</v>
       </c>
       <c r="E8">
-        <v>18.83927196478475</v>
+        <v>11.06324335018592</v>
       </c>
       <c r="F8">
-        <v>14.6</v>
+        <v>11.6</v>
       </c>
       <c r="G8">
-        <v>14.1175179925634</v>
+        <v>9.232894174466566</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>18.83927196478475</v>
+        <v>11.06324335018592</v>
       </c>
       <c r="L8">
-        <v>5.333756871724871</v>
+        <v>3.004822768461589</v>
       </c>
       <c r="M8">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N8">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P8">
-        <v>19.20064674567716</v>
+        <v>13.63288708314677</v>
       </c>
       <c r="Q8">
-        <v>1.019181992890591</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R8">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="S8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T8">
-        <v>0.3613747808924153</v>
+        <v>2.569643732960854</v>
       </c>
       <c r="U8">
-        <v>-0.2006467456771617</v>
+        <v>0.3671129168532268</v>
       </c>
       <c r="V8" t="s">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>14.1175179925634</v>
+        <v>9.232894174466566</v>
       </c>
       <c r="X8">
-        <v>4.721753972221347</v>
+        <v>1.830349175719354</v>
       </c>
       <c r="Y8">
-        <v>0.1607280352152536</v>
+        <v>2.936756649814081</v>
       </c>
       <c r="Z8">
-        <v>0.8852585683558519</v>
+        <v>0.6091371494287687</v>
       </c>
       <c r="AA8">
-        <v>0.03013411354898824</v>
+        <v>0.977347709368444</v>
       </c>
       <c r="AB8">
-        <v>1.088521810556096</v>
+        <v>0.536575494368141</v>
       </c>
       <c r="AC8">
-        <v>55.65685088619063</v>
+        <v>47.8063913390236</v>
       </c>
       <c r="AD8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:30">
@@ -1250,82 +1250,82 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1.12</v>
+        <v>0.228</v>
       </c>
       <c r="D9">
-        <v>1.168</v>
+        <v>0.372</v>
       </c>
       <c r="E9">
-        <v>1.780416614874208</v>
+        <v>0.8817836191054232</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G9">
-        <v>1.142561203557273</v>
+        <v>0.2937625704209726</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>1.780416614874208</v>
+        <v>0.8817836191054232</v>
       </c>
       <c r="L9">
-        <v>0.8500971208676269</v>
+        <v>0.7453408782506382</v>
       </c>
       <c r="M9">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N9">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P9">
-        <v>2.046609860316908</v>
+        <v>0.6936406055835702</v>
       </c>
       <c r="Q9">
-        <v>1.149511773378675</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T9">
-        <v>0.2661932454427003</v>
+        <v>-0.188143013521853</v>
       </c>
       <c r="U9">
-        <v>-0.04660986031690806</v>
+        <v>0.3063593944164298</v>
       </c>
       <c r="V9" t="s">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>1.142561203557273</v>
+        <v>0.2937625704209726</v>
       </c>
       <c r="X9">
-        <v>0.6378554113169352</v>
+        <v>0.5880210486844506</v>
       </c>
       <c r="Y9">
-        <v>0.2195833851257922</v>
+        <v>0.1182163808945768</v>
       </c>
       <c r="Z9">
-        <v>0.7503323980981451</v>
+        <v>0.7889290200539824</v>
       </c>
       <c r="AA9">
-        <v>0.2583038805044779</v>
+        <v>0.1586071344591189</v>
       </c>
       <c r="AB9">
-        <v>1.700194241735254</v>
+        <v>1.242234797084397</v>
       </c>
       <c r="AC9">
-        <v>56.09506097814787</v>
+        <v>56.64783818764582</v>
       </c>
       <c r="AD9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -1336,79 +1336,79 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>0.5600000000000001</v>
+        <v>0.328</v>
       </c>
       <c r="D10">
-        <v>0.408</v>
+        <v>0.212</v>
       </c>
       <c r="E10">
-        <v>0.3147916000487194</v>
+        <v>-0.001836660305252591</v>
       </c>
       <c r="F10">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G10">
-        <v>0.4885561887353032</v>
+        <v>0.275024596049772</v>
       </c>
       <c r="J10" t="s">
         <v>4</v>
       </c>
       <c r="K10">
-        <v>0.3147916000487194</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>0.3921195507989373</v>
+        <v>0.4029126890988887</v>
       </c>
       <c r="M10">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N10">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="O10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P10">
-        <v>0.3618566504167141</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.149511773378675</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R10">
         <v>0</v>
       </c>
       <c r="S10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T10">
-        <v>0.04706505036799469</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>-0.3618566504167141</v>
+        <v>0</v>
       </c>
       <c r="V10" t="s">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>0.4885561887353032</v>
+        <v>0.275024596049772</v>
       </c>
       <c r="X10">
-        <v>0.1737645886865837</v>
+        <v>0.275024596049772</v>
       </c>
       <c r="Y10">
-        <v>0.3147916000487194</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>0.4431418640884933</v>
+        <v>0.682591051338846</v>
       </c>
       <c r="AA10">
-        <v>0.8027949624223952</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.6535325846648956</v>
+        <v>1.007281722747221</v>
       </c>
       <c r="AC10">
-        <v>56.60796713936882</v>
+        <v>64.16680382679213</v>
       </c>
       <c r="AD10" t="s">
         <v>52</v>
@@ -1422,79 +1422,79 @@
         <v>46</v>
       </c>
       <c r="C11">
-        <v>0.74</v>
+        <v>2.432</v>
       </c>
       <c r="D11">
-        <v>0.672</v>
+        <v>1.928</v>
       </c>
       <c r="E11">
-        <v>0.9935995824715044</v>
+        <v>1.608426994139059</v>
       </c>
       <c r="F11">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="G11">
-        <v>0.7080382949605304</v>
+        <v>2.201831003526596</v>
       </c>
       <c r="J11" t="s">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>0.9935995824715044</v>
+        <v>1.608426994139059</v>
       </c>
       <c r="L11">
-        <v>0.3332002265469857</v>
+        <v>1.357115480819956</v>
       </c>
       <c r="M11">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N11">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="O11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P11">
-        <v>1.14215441807513</v>
+        <v>1.265242685482676</v>
       </c>
       <c r="Q11">
-        <v>1.149511773378675</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R11">
         <v>1</v>
       </c>
       <c r="S11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T11">
-        <v>0.1485548356036258</v>
+        <v>-0.3431843086563835</v>
       </c>
       <c r="U11">
-        <v>-0.1421544180751302</v>
+        <v>-0.2652426854826757</v>
       </c>
       <c r="V11" t="s">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>0.7080382949605304</v>
+        <v>2.201831003526596</v>
       </c>
       <c r="X11">
-        <v>0.285561287510974</v>
+        <v>0.5934040093875366</v>
       </c>
       <c r="Y11">
-        <v>0.006400417528495628</v>
+        <v>0.6084269941390592</v>
       </c>
       <c r="Z11">
-        <v>0.8570260904990893</v>
+        <v>0.4372538798459565</v>
       </c>
       <c r="AA11">
-        <v>0.01920892309955583</v>
+        <v>0.4483236708577323</v>
       </c>
       <c r="AB11">
-        <v>0.5553337109116429</v>
+        <v>0.9693682005856831</v>
       </c>
       <c r="AC11">
-        <v>56.90482321607101</v>
+        <v>64.33101602736564</v>
       </c>
       <c r="AD11" t="s">
         <v>52</v>
@@ -1505,82 +1505,82 @@
         <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12">
-        <v>1.904</v>
+        <v>0.752</v>
       </c>
       <c r="D12">
-        <v>1.796</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E12">
-        <v>2.604250820161925</v>
+        <v>0.2483906019674781</v>
       </c>
       <c r="F12">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="G12">
-        <v>1.851874624409452</v>
+        <v>0.6643165727720365</v>
       </c>
       <c r="J12" t="s">
         <v>4</v>
       </c>
       <c r="K12">
-        <v>2.604250820161925</v>
+        <v>0.2483906019674781</v>
       </c>
       <c r="L12">
-        <v>1.198624596172324</v>
+        <v>0.9284964811104729</v>
       </c>
       <c r="M12">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N12">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="O12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P12">
-        <v>2.557215395085126</v>
+        <v>0.1953923886052483</v>
       </c>
       <c r="Q12">
-        <v>0.981938980411313</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T12">
-        <v>-0.04703542507679881</v>
+        <v>-0.05299821336222987</v>
       </c>
       <c r="U12">
-        <v>0.4427846049148738</v>
+        <v>-0.1953923886052483</v>
       </c>
       <c r="V12" t="s">
         <v>6</v>
       </c>
       <c r="W12">
-        <v>1.851874624409452</v>
+        <v>0.6643165727720365</v>
       </c>
       <c r="X12">
-        <v>0.7523761957524733</v>
+        <v>0.4159259708045583</v>
       </c>
       <c r="Y12">
-        <v>0.395749179838075</v>
+        <v>0.2483906019674781</v>
       </c>
       <c r="Z12">
-        <v>0.6276996135029299</v>
+        <v>0.4479564320018907</v>
       </c>
       <c r="AA12">
-        <v>0.3301694134275707</v>
+        <v>0.2675191635302757</v>
       </c>
       <c r="AB12">
-        <v>0.7491403726077025</v>
+        <v>1.031662756789414</v>
       </c>
       <c r="AC12">
-        <v>59.24054223283283</v>
+        <v>68.05844340927169</v>
       </c>
       <c r="AD12" t="s">
         <v>52</v>
@@ -1591,85 +1591,85 @@
         <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C13">
-        <v>8.763999999999999</v>
+        <v>0.896</v>
       </c>
       <c r="D13">
-        <v>6.752</v>
+        <v>0.768</v>
       </c>
       <c r="E13">
-        <v>4.301787319744047</v>
+        <v>1.059965154885961</v>
       </c>
       <c r="F13">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="G13">
-        <v>7.792923558442745</v>
+        <v>0.8375443818480244</v>
       </c>
       <c r="J13" t="s">
         <v>4</v>
       </c>
       <c r="K13">
-        <v>4.301787319744047</v>
+        <v>1.059965154885961</v>
       </c>
       <c r="L13">
-        <v>4.673523904256721</v>
+        <v>0.4515884075301241</v>
       </c>
       <c r="M13">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N13">
-        <v>8.4</v>
+        <v>0.6</v>
       </c>
       <c r="O13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P13">
-        <v>4.224092654695784</v>
+        <v>1.30616174762057</v>
       </c>
       <c r="Q13">
-        <v>0.981938980411313</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T13">
-        <v>-0.07769466504826283</v>
+        <v>0.2461965927346088</v>
       </c>
       <c r="U13">
-        <v>-0.2240926546957844</v>
+        <v>-0.3061617476205698</v>
       </c>
       <c r="V13" t="s">
         <v>6</v>
       </c>
       <c r="W13">
-        <v>7.792923558442745</v>
+        <v>0.8375443818480244</v>
       </c>
       <c r="X13">
-        <v>3.491136238698697</v>
+        <v>0.2224207730379366</v>
       </c>
       <c r="Y13">
-        <v>0.3017873197440473</v>
+        <v>0.05996515488596099</v>
       </c>
       <c r="Z13">
-        <v>0.747002970396474</v>
+        <v>0.4925298553486442</v>
       </c>
       <c r="AA13">
-        <v>0.06457382607354901</v>
+        <v>0.1327871882582834</v>
       </c>
       <c r="AB13">
-        <v>0.5563718933638954</v>
+        <v>0.7526473458835402</v>
       </c>
       <c r="AC13">
-        <v>60.16058574846904</v>
+        <v>69.3073016888561</v>
       </c>
       <c r="AD13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:30">
@@ -1677,85 +1677,85 @@
         <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14">
-        <v>173.496</v>
+        <v>0.856</v>
       </c>
       <c r="D14">
-        <v>170.784</v>
+        <v>1.468</v>
       </c>
       <c r="E14">
-        <v>173.6497555759981</v>
+        <v>-0.6136915121990012</v>
       </c>
       <c r="F14">
-        <v>169.2</v>
+        <v>2.4</v>
       </c>
       <c r="G14">
-        <v>172.1870739018374</v>
+        <v>1.135490924289134</v>
       </c>
       <c r="J14" t="s">
         <v>4</v>
       </c>
       <c r="K14">
-        <v>173.6497555759981</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>4.764861070548267</v>
+        <v>2.225665663703473</v>
       </c>
       <c r="M14">
-        <v>5.24749619700716</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N14">
-        <v>13.2</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P14">
-        <v>176.9807039529099</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>1.019181992890591</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R14">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="S14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T14">
-        <v>3.330948376911721</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>0.01929604709013688</v>
+        <v>0</v>
       </c>
       <c r="V14" t="s">
         <v>6</v>
       </c>
       <c r="W14">
-        <v>172.1870739018374</v>
+        <v>1.135490924289134</v>
       </c>
       <c r="X14">
-        <v>1.462681674160791</v>
+        <v>1.135490924289134</v>
       </c>
       <c r="Y14">
-        <v>3.350244424001858</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>0.3069725753814032</v>
+        <v>0.5101803666233026</v>
       </c>
       <c r="AA14">
-        <v>0.7031148179135396</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.3609743235263839</v>
+        <v>0.7179566657107976</v>
       </c>
       <c r="AC14">
-        <v>64.04255765445993</v>
+        <v>71.77620020831648</v>
       </c>
       <c r="AD14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:30">
@@ -1766,79 +1766,79 @@
         <v>46</v>
       </c>
       <c r="C15">
-        <v>0.6879999999999999</v>
+        <v>1.032</v>
       </c>
       <c r="D15">
-        <v>0.608</v>
+        <v>1.224</v>
       </c>
       <c r="E15">
-        <v>-0.01550360442781762</v>
+        <v>0.883771840094469</v>
       </c>
       <c r="F15">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="G15">
-        <v>0.6503979940712121</v>
+        <v>1.119683427227963</v>
       </c>
       <c r="J15" t="s">
         <v>4</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>0.883771840094469</v>
       </c>
       <c r="L15">
-        <v>1.005444112310955</v>
+        <v>0.9957719791398976</v>
       </c>
       <c r="M15">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N15">
         <v>0.9</v>
       </c>
       <c r="O15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>0.6952046069791448</v>
       </c>
       <c r="Q15">
-        <v>0.8540406002469759</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>-0.1885672331153242</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>0.3047953930208552</v>
       </c>
       <c r="V15" t="s">
         <v>6</v>
       </c>
       <c r="W15">
-        <v>0.6503979940712121</v>
+        <v>1.119683427227963</v>
       </c>
       <c r="X15">
-        <v>0.6503979940712121</v>
+        <v>0.2359115871334945</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>0.116228159905531</v>
       </c>
       <c r="Z15">
-        <v>0.6468763266973739</v>
+        <v>0.2369132613444939</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>0.1167216615252858</v>
       </c>
       <c r="AB15">
-        <v>1.117160124789949</v>
+        <v>1.106413310155442</v>
       </c>
       <c r="AC15">
-        <v>65.67383349516004</v>
+        <v>82.29612186002319</v>
       </c>
       <c r="AD15" t="s">
         <v>53</v>
@@ -1852,79 +1852,79 @@
         <v>46</v>
       </c>
       <c r="C16">
-        <v>0.38</v>
+        <v>0.288</v>
       </c>
       <c r="D16">
-        <v>0.496</v>
+        <v>0.408</v>
       </c>
       <c r="E16">
-        <v>0.7868170324027036</v>
+        <v>0.7561917677339507</v>
       </c>
       <c r="F16">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G16">
-        <v>0.4345229085967423</v>
+        <v>0.3428021420174772</v>
       </c>
       <c r="J16" t="s">
         <v>4</v>
       </c>
       <c r="K16">
-        <v>0.7868170324027036</v>
+        <v>0.7561917677339507</v>
       </c>
       <c r="L16">
-        <v>0.8079772006265793</v>
+        <v>1.908933484234525</v>
       </c>
       <c r="M16">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N16">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="O16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P16">
-        <v>0.6719736906377493</v>
+        <v>0.5948458378489989</v>
       </c>
       <c r="Q16">
-        <v>0.8540406002469759</v>
+        <v>0.7866335805685235</v>
       </c>
       <c r="R16">
         <v>1</v>
       </c>
       <c r="S16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T16">
-        <v>-0.1148433417649544</v>
+        <v>-0.1613459298849518</v>
       </c>
       <c r="U16">
-        <v>0.3280263093622507</v>
+        <v>0.4051541621510011</v>
       </c>
       <c r="V16" t="s">
         <v>6</v>
       </c>
       <c r="W16">
-        <v>0.4345229085967423</v>
+        <v>0.3428021420174772</v>
       </c>
       <c r="X16">
-        <v>0.3522941238059614</v>
+        <v>0.4133896257164735</v>
       </c>
       <c r="Y16">
-        <v>0.2131829675972964</v>
+        <v>0.2438082322660493</v>
       </c>
       <c r="Z16">
-        <v>0.4360198821609822</v>
+        <v>0.2165552802811467</v>
       </c>
       <c r="AA16">
-        <v>0.2638477514365193</v>
+        <v>0.1277196058844426</v>
       </c>
       <c r="AB16">
-        <v>1.346628667710966</v>
+        <v>1.590777903528771</v>
       </c>
       <c r="AC16">
-        <v>68.6767387081441</v>
+        <v>83.07197425634185</v>
       </c>
       <c r="AD16" t="s">
         <v>53</v>

--- a/outputs/Block5_Least_Stable.xlsx
+++ b/outputs/Block5_Least_Stable.xlsx
@@ -544,37 +544,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>52.9566065934066</v>
+        <v>52.80457815565729</v>
       </c>
       <c r="F2" t="n">
-        <v>52.9566065934066</v>
+        <v>52.8045781556573</v>
       </c>
       <c r="G2" t="n">
-        <v>53.00842857142858</v>
+        <v>52.85625136254632</v>
       </c>
       <c r="H2" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09418669952721606</v>
+        <v>0.09391630726254439</v>
       </c>
       <c r="J2" t="n">
-        <v>52.80386813186814</v>
+        <v>52.65227817745804</v>
       </c>
       <c r="K2" t="n">
-        <v>53.02206593406594</v>
+        <v>52.86984957488554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2181978021978068</v>
+        <v>0.2175713974275055</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1527384615384619</v>
+        <v>0.1522999781992525</v>
       </c>
       <c r="N2" t="n">
         <v>1.323492690170848</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1154055951142013</v>
+        <v>0.1150742873990428</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -612,37 +612,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>44.1233934065934</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="F3" t="n">
-        <v>44.12339340659342</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="G3" t="n">
-        <v>44.16657142857143</v>
+        <v>44.31874863745368</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07847626697110505</v>
+        <v>0.07874665923576957</v>
       </c>
       <c r="J3" t="n">
-        <v>43.99613186813187</v>
+        <v>44.14772182254198</v>
       </c>
       <c r="K3" t="n">
-        <v>44.17793406593407</v>
+        <v>44.33015042511447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1818021978021989</v>
+        <v>0.1824286025724859</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1272615384615321</v>
+        <v>0.1277000218007345</v>
       </c>
       <c r="N3" t="n">
         <v>1.064148394560983</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1195900300296315</v>
+        <v>0.1200020809629821</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
@@ -1213,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-dd0af9f21104-20261020T060932Z</t>
+          <t>2026-69084551907b-20261024T072445Z</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dd0af9f211044926f193d3ea436dabde2b2960f060ab768c53232e3e59f37c10</t>
+          <t>69084551907b520052181adf33e09563f086f0b6de4f1d95d2e192b06c14159d</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T02:41:23.457320+00:00</t>
+          <t>2026-10-24T07:22:07.989106+00:00</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20T06:09:32.147340+00:00</t>
+          <t>2026-10-24T07:24:45.840036+00:00</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20T06:11:56.240312+00:00</t>
+          <t>2026-10-24T07:26:59.123079+00:00</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>35-race structural motor + polling enrichment on 12 monitored races</t>
+          <t>35-race structural motor + polling enrichment on 15 monitored races</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,53 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Public Senate map highlights 12 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+          <t>Public Senate map highlights 15 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration source</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Recovered Model(5).xlsx / Senate Historic</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration rows</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration reference SHA256</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7b3f807a5128485c7fd4de43f99733784af9627e835db4777c047b68e762feb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senate production policy</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Recovered 5B calibration + 15 current monitored races; automatic structural blending disabled</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1702,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-dd0af9f21104-20261020T060932Z</t>
+          <t>2026-69084551907b-20261024T072445Z</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6254f3f54af6754b67deae4c4b8445dd2c4a92fbbcded33cef106f4df9255f2a</t>
+          <t>8a7bfde9efafe267b78417530287877a5e160939951e8ae39d62138f60d4e05a</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1738,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T06:12:00.987520+00:00</t>
+          <t>2026-10-24T07:27:04.098692+00:00</t>
         </is>
       </c>
     </row>
